--- a/Data/g13.7.xlsx
+++ b/Data/g13.7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,16 +978,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Empregador</t>
+          <t>Conta própria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3.8</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="29">
@@ -998,16 +998,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Empregador</t>
+          <t>Conta própria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.4</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="30">
@@ -1018,16 +1018,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Empregador</t>
+          <t>Conta própria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="31">
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empregador</t>
+          <t>Conta própria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.2</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="32">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="33">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="34">
@@ -1103,11 +1103,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="35">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="36">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="37">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="38">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="40">
@@ -1223,11 +1223,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="44">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="46">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="47">
@@ -1363,11 +1363,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="48">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="49">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="51">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="52">
@@ -1463,11 +1463,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="53">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1498,16 +1498,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="55">
@@ -1518,16 +1518,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="56">
@@ -1538,16 +1538,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="57">
@@ -1558,16 +1558,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="58">
@@ -1578,16 +1578,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="59">
@@ -1598,16 +1598,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1618,16 +1618,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="61">
@@ -1638,16 +1638,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Setor privado com carteira</t>
+          <t>Empregador</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="62">
@@ -1663,11 +1663,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="63">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>23.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="65">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="66">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>26.4</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="67">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>26.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="68">
@@ -1783,11 +1783,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="69">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="70">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="71">
@@ -1843,11 +1843,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.4</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="72">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27.3</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="73">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>28.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -1903,11 +1903,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>29.3</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="75">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30.2</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="76">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>30</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="77">
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.4</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="78">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30.7</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="79">
@@ -2003,11 +2003,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30.4</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="80">
@@ -2018,16 +2018,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>22.2</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="81">
@@ -2038,16 +2038,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21.9</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="82">
@@ -2058,16 +2058,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.8</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="83">
@@ -2078,16 +2078,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>24.1</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="84">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>23.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -2118,16 +2118,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21.1</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="86">
@@ -2138,16 +2138,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21.1</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="87">
@@ -2158,16 +2158,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>22.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="88">
@@ -2178,16 +2178,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.7</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="89">
@@ -2198,16 +2198,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22.7</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="90">
@@ -2218,16 +2218,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>24.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="91">
@@ -2238,16 +2238,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Setor privado sem carteira</t>
+          <t>Setor privado com carteira</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.8</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="92">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24.9</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="93">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="94">
@@ -2303,11 +2303,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="95">
@@ -2323,11 +2323,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="96">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>25.7</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="97">
@@ -2363,11 +2363,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>24.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="98">
@@ -2383,11 +2383,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>24.5</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="99">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>25.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="100">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>24.3</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="101">
@@ -2443,11 +2443,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>23.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="102">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="103">
@@ -2483,11 +2483,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="104">
@@ -2503,11 +2503,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="105">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="106">
@@ -2538,16 +2538,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>14</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="107">
@@ -2558,16 +2558,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>14</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="108">
@@ -2578,16 +2578,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>13.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="109">
@@ -2598,16 +2598,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>13.7</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="110">
@@ -2618,16 +2618,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>13.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="111">
@@ -2638,16 +2638,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="112">
@@ -2658,16 +2658,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15.1</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="113">
@@ -2678,16 +2678,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>14.2</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="114">
@@ -2698,16 +2698,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>14.9</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="115">
@@ -2718,16 +2718,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16.8</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="116">
@@ -2738,16 +2738,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="117">
@@ -2758,16 +2758,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>14.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="118">
@@ -2778,16 +2778,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>13.5</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="119">
@@ -2798,16 +2798,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="120">
@@ -2818,16 +2818,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>15</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="121">
@@ -2838,16 +2838,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Setor público</t>
+          <t>Setor privado sem carteira</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>15.3</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="122">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="125">
@@ -2923,11 +2923,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="126">
@@ -2943,11 +2943,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>15.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="127">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="128">
@@ -2983,11 +2983,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="129">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="130">
@@ -3023,11 +3023,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="131">
@@ -3043,11 +3043,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>14.3</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="132">
@@ -3058,16 +3058,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="133">
@@ -3078,16 +3078,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="134">
@@ -3098,16 +3098,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="135">
@@ -3118,16 +3118,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="136">
@@ -3138,16 +3138,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
@@ -3158,16 +3158,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="138">
@@ -3178,16 +3178,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3.1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="139">
@@ -3198,16 +3198,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="140">
@@ -3218,16 +3218,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="141">
@@ -3238,16 +3238,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3.3</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="142">
@@ -3258,16 +3258,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="143">
@@ -3278,16 +3278,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="144">
@@ -3298,16 +3298,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="145">
@@ -3318,16 +3318,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3.1</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="146">
@@ -3338,16 +3338,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="147">
@@ -3358,16 +3358,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="148">
@@ -3378,16 +3378,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3.3</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="149">
@@ -3398,16 +3398,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.9</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="150">
@@ -3418,16 +3418,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="151">
@@ -3438,16 +3438,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Trabalhador familiar auxiliar</t>
+          <t>Setor público</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="152">
@@ -3463,11 +3463,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="153">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="154">
@@ -3503,11 +3503,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="155">
@@ -3523,11 +3523,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="156">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="157">
@@ -3563,11 +3563,491 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D157" t="n">
         <v>2.1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>01/07/2020</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>01/10/2020</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>01/07/2021</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>01/10/2021</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>01/04/2022</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>01/07/2022</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>01/10/2022</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>01/04/2023</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>01/07/2023</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>01/04/2025</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Trabalhador familiar auxiliar</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
